--- a/Unity/Assets/Config/Excel/StoryEndingConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StoryEndingConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
   <si>
     <t>##var</t>
   </si>
@@ -91,7 +91,7 @@
     <t>描述</t>
   </si>
   <si>
-    <t>亲和下限，-1表示不限制</t>
+    <t>亲和下限</t>
   </si>
   <si>
     <t>亲和上限</t>
@@ -118,10 +118,16 @@
     <t>最亲和的人</t>
   </si>
   <si>
+    <t>1;1000</t>
+  </si>
+  <si>
     <t>结局2</t>
   </si>
   <si>
     <t>最有趣的人</t>
+  </si>
+  <si>
+    <t>1;2000</t>
   </si>
   <si>
     <t>结局3</t>
@@ -130,10 +136,16 @@
     <t>最有劲的人</t>
   </si>
   <si>
+    <t>1;3000</t>
+  </si>
+  <si>
     <t>结局5</t>
   </si>
   <si>
     <t>平庸的人</t>
+  </si>
+  <si>
+    <t>1;4000</t>
   </si>
 </sst>
 </file>
@@ -11320,7 +11332,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{2C9F55AC-5988-47F0-B7C7-D5BA5FC28C56}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{E973BC18-1072-4EA0-9D23-A3158D5D8EAC}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -11626,9 +11638,9 @@
     <col min="2" max="2" width="17.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="22" style="3" customWidth="1"/>
     <col min="4" max="4" width="39.125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.5" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.25" style="3" customWidth="1"/>
-    <col min="7" max="10" width="12.375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="19" style="3" customWidth="1"/>
+    <col min="6" max="7" width="13.375" style="3" customWidth="1"/>
+    <col min="8" max="10" width="12.375" style="3" customWidth="1"/>
     <col min="11" max="11" width="24.625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11766,52 +11778,122 @@
       <c r="D5" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="E5" s="3">
+        <v>60</v>
+      </c>
+      <c r="F5" s="3">
+        <v>100</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>100</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <v>30</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="6" customFormat="1" spans="1:11">
       <c r="B6" s="2">
         <v>1002</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>100</v>
+      </c>
+      <c r="G6" s="3">
+        <v>60</v>
+      </c>
+      <c r="H6" s="3">
+        <v>100</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3">
+        <v>30</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="7" customFormat="1" spans="1:11">
       <c r="B7" s="2">
         <v>1003</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>100</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>100</v>
+      </c>
+      <c r="I7" s="3">
+        <v>60</v>
+      </c>
+      <c r="J7" s="3">
+        <v>100</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="8" spans="1:11">
       <c r="B8" s="2">
         <v>1005</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>100</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>100</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>100</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
